--- a/auto_watch.xlsx
+++ b/auto_watch.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -428,20 +428,25 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>channel_count</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>like</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>search</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>like_comment_count</t>
         </is>
@@ -453,22 +458,25 @@
           <t>a;b;c;d;e;f;g;h;j</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>false;This took most of the day and required multiple approaches and many failed attempts, but I did eventually get it installed via the very cool stable-diffusion-webui project. Excited, I immediately start generating a picture of a litter of kittens cuddling and sleeping together, because what else could I possibly generate?;Suddenly the microwave timer goes off. Food is done I guess. I didn't realize my partner was heating up dinner already, it is a little early for that. Microwave's tone sounds a bit off too, I hope it isn't broken or something.;false;This took most of the day and required multiple approaches and many failed attempts, but I did eventually get it installed via the very cool stable-diffusion-webui project. Excited, I immediately start generating a picture of a litter of kittens cuddling and sleeping together, because what else could I possibly generate?</t>
-        </is>
+      <c r="B2" t="n">
+        <v>9</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>false;false;false;false;false</t>
+          <t>false;false;false;false;Suddenly the microwave timer goes off. Food is done I guess. I didn't realize my partner was heating up dinner already, it is a little early for that. Microwave's tone sounds a bit off too, I hope it isn't broken or something.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>def;false;123;123;123</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+          <t>false;false;false;true;false</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>false;def;def;false;def</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -478,22 +486,25 @@
           <t>a;b;c;d;e;f;g;h;j</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>But more importantly, I now have a cute (if a little creepy) picture of kittens!;false;But more importantly, I now have a cute (if a little creepy) picture of kittens!;false;This took most of the day and required multiple approaches and many failed attempts, but I did eventually get it installed via the very cool stable-diffusion-webui project. Excited, I immediately start generating a picture of a litter of kittens cuddling and sleeping together, because what else could I possibly generate?</t>
-        </is>
+      <c r="B3" t="n">
+        <v>9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>false;But more importantly, I now have a cute (if a little creepy) picture of kittens!;false;Suddenly the microwave timer goes off. Food is done I guess. I didn't realize my partner was heating up dinner already, it is a little early for that. Microwave's tone sounds a bit off too, I hope it isn't broken or something.;Suddenly the microwave timer goes off. Food is done I guess. I didn't realize my partner was heating up dinner already, it is a little early for that. Microwave's tone sounds a bit off too, I hope it isn't broken or something.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>false;false;false;false;false</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>def;false;false;123;def</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>123;false;def;123;false</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>5</v>
       </c>
     </row>

--- a/auto_watch.xlsx
+++ b/auto_watch.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Watch" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watch" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,25 +455,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>a;b;c;d;e;f;g;h;j</t>
+          <t>Immerse yourself in next-gen strategy battles;Mini Unboxing Toys;Nerd Odyssey;ちび世界 / Chibisekai;Solace Night;Play Foundation: Galactic Frontier (FGF);Make your mark in the universe, Unveil the secrets of the galaxy;BaBy Turtle Tin;Shayan Quran Recitation;Mickey Unboxing;10HoursMovies;Pinkish;Walk Your Way Slim;Small steps, big results. Let's walk together towards a healthier future. Take a quiz;달밤의 오보에 Moonlight Oboe;Киноконцерн "Мосфильм";Toy Playset;Arknights: Endfield is officially released! Claim your exclusive benefits now;Xavier Outside;CUTE DİSNEY LOVE;My Cute Toys;MONO BIBI ESP;Disney Suprise Box;Craft a Winning Resume;Use AI and expert tips to craft a winning resume for 2026.;Mr Bean;ENHYPEN;Sochill;Genshin Impact;PvZ Mini ASMR;SpongeBob SquarePants Official;Bloom In Style With The Spring Summer Collection;Lofi Girl;7 Asian;Dreamy creative toys;Relax Your Soul;Gatitos y Perritos TV;Owl Lo-Fi Music;Daniel Sfilms;DocumentDisney;روائع المدح;Unboxing COA Toys;SoraRadio;Moomin Official;The Grand Terrace - Music And Jazz Scapes;The Wall Street Journal;The Tonight Show Starring Jimmy Fallon;Demon Music - Español;TomTom SLIME;Magnet ASMR</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>false;false;false;false;Suddenly the microwave timer goes off. Food is done I guess. I didn't realize my partner was heating up dinner already, it is a little early for that. Microwave's tone sounds a bit off too, I hope it isn't broken or something.</t>
+          <t>This took most of the day and required multiple approaches and many failed attempts, but I did eventually get it installed via the very cool stable-diffusion-webui project. Excited, I immediately start generating a picture of a litter of kittens cuddling and sleeping together, because what else could I possibly generate?;This took most of the day and required multiple approaches and many failed attempts, but I did eventually get it installed via the very cool stable-diffusion-webui project. Excited, I immediately start generating a picture of a litter of kittens cuddling and sleeping together, because what else could I possibly generate?;This took most of the day and required multiple approaches and many failed attempts, but I did eventually get it installed via the very cool stable-diffusion-webui project. Excited, I immediately start generating a picture of a litter of kittens cuddling and sleeping together, because what else could I possibly generate?;This took most of the day and required multiple approaches and many failed attempts, but I did eventually get it installed via the very cool stable-diffusion-webui project. Excited, I immediately start generating a picture of a litter of kittens cuddling and sleeping together, because what else could I possibly generate?;Suddenly the microwave timer goes off. Food is done I guess. I didn't realize my partner was heating up dinner already, it is a little early for that. Microwave's tone sounds a bit off too, I hope it isn't broken or something.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>false;false;false;true;false</t>
+          <t>true;true;true;true;true</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>false;def;def;false;def</t>
+          <t>false;def;123;false;false</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -483,25 +483,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>a;b;c;d;e;f;g;h;j</t>
+          <t>Immerse yourself in next-gen strategy battles;Mini Unboxing Toys;Nerd Odyssey;ちび世界 / Chibisekai;Solace Night;Play Foundation: Galactic Frontier (FGF);Make your mark in the universe, Unveil the secrets of the galaxy;BaBy Turtle Tin;Shayan Quran Recitation;Mickey Unboxing;10HoursMovies;Pinkish;Walk Your Way Slim;Small steps, big results. Let's walk together towards a healthier future. Take a quiz;달밤의 오보에 Moonlight Oboe;Киноконцерн "Мосфильм";Toy Playset;Arknights: Endfield is officially released! Claim your exclusive benefits now;Xavier Outside;CUTE DİSNEY LOVE;My Cute Toys;MONO BIBI ESP;Disney Suprise Box;Craft a Winning Resume;Use AI and expert tips to craft a winning resume for 2026.;Mr Bean;ENHYPEN;Sochill;Genshin Impact;PvZ Mini ASMR;SpongeBob SquarePants Official;Bloom In Style With The Spring Summer Collection;Lofi Girl;7 Asian;Dreamy creative toys;Relax Your Soul;Gatitos y Perritos TV;Owl Lo-Fi Music;Daniel Sfilms;DocumentDisney;روائع المدح;Unboxing COA Toys;SoraRadio;Moomin Official;The Grand Terrace - Music And Jazz Scapes;The Wall Street Journal;The Tonight Show Starring Jimmy Fallon;Demon Music - Español;TomTom SLIME;Magnet ASMR</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>false;But more importantly, I now have a cute (if a little creepy) picture of kittens!;false;Suddenly the microwave timer goes off. Food is done I guess. I didn't realize my partner was heating up dinner already, it is a little early for that. Microwave's tone sounds a bit off too, I hope it isn't broken or something.;Suddenly the microwave timer goes off. Food is done I guess. I didn't realize my partner was heating up dinner already, it is a little early for that. Microwave's tone sounds a bit off too, I hope it isn't broken or something.</t>
+          <t>This took most of the day and required multiple approaches and many failed attempts, but I did eventually get it installed via the very cool stable-diffusion-webui project. Excited, I immediately start generating a picture of a litter of kittens cuddling and sleeping together, because what else could I possibly generate?;But more importantly, I now have a cute (if a little creepy) picture of kittens!;Suddenly the microwave timer goes off. Food is done I guess. I didn't realize my partner was heating up dinner already, it is a little early for that. Microwave's tone sounds a bit off too, I hope it isn't broken or something.;But more importantly, I now have a cute (if a little creepy) picture of kittens!;This took most of the day and required multiple approaches and many failed attempts, but I did eventually get it installed via the very cool stable-diffusion-webui project. Excited, I immediately start generating a picture of a litter of kittens cuddling and sleeping together, because what else could I possibly generate?</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>false;false;false;false;false</t>
+          <t>true;true;true;true;true</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>123;false;def;123;false</t>
+          <t>siuu;123;def;false;false</t>
         </is>
       </c>
       <c r="F3" t="n">
